--- a/data/trans_orig/Predimed_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según adherencia a la dieta mediterránea en 2023</t>
+          <t>Población según adherencia a la dieta mediterránea en 2023 (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43290</t>
+          <t>42933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52259</t>
+          <t>51615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38049</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82991</t>
+          <t>85575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301197</t>
+          <t>301554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334520</t>
+          <t>334332</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226669</t>
+          <t>227313</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256591</t>
+          <t>256715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540423</t>
+          <t>537839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>585365</t>
+          <t>585285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42213</t>
+          <t>42239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82704</t>
+          <t>82731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42218</t>
+          <t>37298</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89211</t>
+          <t>86778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94561</t>
+          <t>94479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156542</t>
+          <t>157360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>321355</t>
+          <t>321328</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>361846</t>
+          <t>361820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392771</t>
+          <t>395204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439764</t>
+          <t>444684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729498</t>
+          <t>728680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>791479</t>
+          <t>791561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78639</t>
+          <t>76813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119435</t>
+          <t>114117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76873</t>
+          <t>78198</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106295</t>
+          <t>108161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165228</t>
+          <t>164441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212225</t>
+          <t>213002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>389432</t>
+          <t>394750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430228</t>
+          <t>432054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>411096</t>
+          <t>409230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>440518</t>
+          <t>439193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>814033</t>
+          <t>813256</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>861030</t>
+          <t>861817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47681</t>
+          <t>45632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157294</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139579</t>
+          <t>141313</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260510</t>
+          <t>264684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177701</t>
+          <t>170800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>360832</t>
+          <t>367640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>693517</t>
+          <t>695869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>803130</t>
+          <t>805179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>423464</t>
+          <t>419290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>544395</t>
+          <t>542661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1173953</t>
+          <t>1167145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1357084</t>
+          <t>1363985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83771</t>
+          <t>80646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117512</t>
+          <t>116358</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90101</t>
+          <t>90134</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118155</t>
+          <t>116094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183760</t>
+          <t>182315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226866</t>
+          <t>225909</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405254</t>
+          <t>406408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438995</t>
+          <t>442120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402265</t>
+          <t>404326</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>430319</t>
+          <t>430286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>816320</t>
+          <t>817277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859426</t>
+          <t>860871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73271</t>
+          <t>72695</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98303</t>
+          <t>99682</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37214</t>
+          <t>37247</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>158175</t>
+          <t>157507</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>94249</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>245101</t>
+          <t>245507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241257</t>
+          <t>239878</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266289</t>
+          <t>266865</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>434092</t>
+          <t>434760</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>555053</t>
+          <t>555020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>686726</t>
+          <t>686320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>839458</t>
+          <t>837578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37616</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58485</t>
+          <t>58020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56664</t>
+          <t>55801</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77395</t>
+          <t>77910</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99809</t>
+          <t>98714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128660</t>
+          <t>128401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197328</t>
+          <t>197793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>218197</t>
+          <t>217661</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309370</t>
+          <t>308855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330101</t>
+          <t>330964</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>513918</t>
+          <t>514177</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>542769</t>
+          <t>543864</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>390986</t>
+          <t>396623</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>577176</t>
+          <t>579041</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515132</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>727904</t>
+          <t>721511</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>990921</t>
+          <t>986434</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1266726</t>
+          <t>1258894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2649186</t>
+          <t>2647321</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2835376</t>
+          <t>2829739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2733822</t>
+          <t>2740215</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2946526</t>
+          <t>2946594</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5421362</t>
+          <t>5429194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5697167</t>
+          <t>5701654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Predimed_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22342</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42933</t>
+          <t>43947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>43575</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22213</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51615</t>
+          <t>63014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57197</t>
+          <t>66657</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>46910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85575</t>
+          <t>92768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>322145</t>
+          <t>330938</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301554</t>
+          <t>310073</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334332</t>
+          <t>343419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>244072</t>
+          <t>283002</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227313</t>
+          <t>263563</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256715</t>
+          <t>297703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>566217</t>
+          <t>613940</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537839</t>
+          <t>587829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>585285</t>
+          <t>633687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>344487</t>
+          <t>354020</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>344487</t>
+          <t>354020</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>344487</t>
+          <t>354020</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>278928</t>
+          <t>326577</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>278928</t>
+          <t>326577</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>278928</t>
+          <t>326577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>623414</t>
+          <t>680597</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>623414</t>
+          <t>680597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>623414</t>
+          <t>680597</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61466</t>
+          <t>72791</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42239</t>
+          <t>53301</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82731</t>
+          <t>94390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66799</t>
+          <t>73126</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37298</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86778</t>
+          <t>92893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>128265</t>
+          <t>145917</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94479</t>
+          <t>121263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157360</t>
+          <t>176066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>342593</t>
+          <t>379392</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>321328</t>
+          <t>357793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>361820</t>
+          <t>398882</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>415183</t>
+          <t>391125</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>395204</t>
+          <t>371358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444684</t>
+          <t>407191</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>757775</t>
+          <t>770517</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728680</t>
+          <t>740368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>791561</t>
+          <t>795171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>404059</t>
+          <t>452183</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>404059</t>
+          <t>452183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>404059</t>
+          <t>452183</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>481982</t>
+          <t>464251</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>481982</t>
+          <t>464251</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>481982</t>
+          <t>464251</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>886040</t>
+          <t>916434</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>886040</t>
+          <t>916434</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>886040</t>
+          <t>916434</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95670</t>
+          <t>106899</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76813</t>
+          <t>87530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114117</t>
+          <t>128612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91695</t>
+          <t>104696</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78198</t>
+          <t>89623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108161</t>
+          <t>120795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>187365</t>
+          <t>211595</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164441</t>
+          <t>186629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213002</t>
+          <t>237994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>413197</t>
+          <t>480153</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>394750</t>
+          <t>458440</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>432054</t>
+          <t>499522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425696</t>
+          <t>487338</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>409230</t>
+          <t>471239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439193</t>
+          <t>502411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>838893</t>
+          <t>967491</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>941092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>861817</t>
+          <t>992457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>508867</t>
+          <t>587052</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>508867</t>
+          <t>587052</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>508867</t>
+          <t>587052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>517391</t>
+          <t>592034</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>517391</t>
+          <t>592034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>517391</t>
+          <t>592034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1026258</t>
+          <t>1179086</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1026258</t>
+          <t>1179086</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1026258</t>
+          <t>1179086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>104996</t>
+          <t>115984</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45632</t>
+          <t>98170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154942</t>
+          <t>138558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>173336</t>
+          <t>146792</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141313</t>
+          <t>129126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>264684</t>
+          <t>164209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>278331</t>
+          <t>262776</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170800</t>
+          <t>238044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>367640</t>
+          <t>289594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>745815</t>
+          <t>544084</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>695869</t>
+          <t>521510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>805179</t>
+          <t>561898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>510638</t>
+          <t>559477</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>419290</t>
+          <t>542060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>542661</t>
+          <t>577143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1256454</t>
+          <t>1103561</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1167145</t>
+          <t>1076743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1363985</t>
+          <t>1128293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>850811</t>
+          <t>660068</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>850811</t>
+          <t>660068</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>850811</t>
+          <t>660068</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>683974</t>
+          <t>706269</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>683974</t>
+          <t>706269</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>683974</t>
+          <t>706269</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1534785</t>
+          <t>1366337</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1534785</t>
+          <t>1366337</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1534785</t>
+          <t>1366337</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>99785</t>
+          <t>109213</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>92114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116358</t>
+          <t>129067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>102804</t>
+          <t>114575</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90134</t>
+          <t>100543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116094</t>
+          <t>129806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>202589</t>
+          <t>223788</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182315</t>
+          <t>201531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225909</t>
+          <t>249854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>422981</t>
+          <t>458927</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>406408</t>
+          <t>439073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>442120</t>
+          <t>476026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>417616</t>
+          <t>464145</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>404326</t>
+          <t>448914</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>430286</t>
+          <t>478177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>840597</t>
+          <t>923073</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>817277</t>
+          <t>897007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>860871</t>
+          <t>945330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>522766</t>
+          <t>568140</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>522766</t>
+          <t>568140</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>522766</t>
+          <t>568140</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>520420</t>
+          <t>578720</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>520420</t>
+          <t>578720</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>520420</t>
+          <t>578720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1043186</t>
+          <t>1146861</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1043186</t>
+          <t>1146861</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1043186</t>
+          <t>1146861</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85344</t>
+          <t>97976</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72695</t>
+          <t>84728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99682</t>
+          <t>112662</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>99763</t>
+          <t>107302</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37247</t>
+          <t>94951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>157507</t>
+          <t>119856</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>185106</t>
+          <t>205278</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94249</t>
+          <t>187517</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>245507</t>
+          <t>226179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>254216</t>
+          <t>278031</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239878</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266865</t>
+          <t>291279</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>492504</t>
+          <t>313826</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>434760</t>
+          <t>301272</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>555020</t>
+          <t>326177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>746721</t>
+          <t>591856</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>686320</t>
+          <t>570955</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>837578</t>
+          <t>609617</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>339560</t>
+          <t>376007</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>339560</t>
+          <t>376007</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>339560</t>
+          <t>376007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>592267</t>
+          <t>421128</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>592267</t>
+          <t>421128</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>592267</t>
+          <t>421128</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>931827</t>
+          <t>797134</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>931827</t>
+          <t>797134</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>931827</t>
+          <t>797134</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46917</t>
+          <t>51530</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>41295</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58020</t>
+          <t>62849</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>66065</t>
+          <t>74122</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55801</t>
+          <t>62397</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77910</t>
+          <t>86900</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>112982</t>
+          <t>125652</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98714</t>
+          <t>108919</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128401</t>
+          <t>141350</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>208896</t>
+          <t>228291</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197793</t>
+          <t>216972</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217661</t>
+          <t>238526</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>320700</t>
+          <t>348454</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>308855</t>
+          <t>335676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330964</t>
+          <t>360179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>529596</t>
+          <t>576744</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>514177</t>
+          <t>561046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>543864</t>
+          <t>593477</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>255813</t>
+          <t>279821</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>255813</t>
+          <t>279821</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>255813</t>
+          <t>279821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>386765</t>
+          <t>422576</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>386765</t>
+          <t>422576</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>386765</t>
+          <t>422576</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>642578</t>
+          <t>702396</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>642578</t>
+          <t>702396</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>642578</t>
+          <t>702396</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>516519</t>
+          <t>577475</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>396623</t>
+          <t>533687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>579041</t>
+          <t>631365</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>635318</t>
+          <t>664187</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>515132</t>
+          <t>625674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>721511</t>
+          <t>707948</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1151836</t>
+          <t>1241662</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>986434</t>
+          <t>1175345</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1258894</t>
+          <t>1310511</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2709843</t>
+          <t>2699816</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2647321</t>
+          <t>2645926</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2829739</t>
+          <t>2743604</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2826408</t>
+          <t>2847367</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2740215</t>
+          <t>2803606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2946594</t>
+          <t>2885880</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5536252</t>
+          <t>5547183</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5429194</t>
+          <t>5478334</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5701654</t>
+          <t>5613500</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3226362</t>
+          <t>3277291</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3226362</t>
+          <t>3277291</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3226362</t>
+          <t>3277291</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3461726</t>
+          <t>3511554</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3461726</t>
+          <t>3511554</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3461726</t>
+          <t>3511554</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6688088</t>
+          <t>6788845</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6688088</t>
+          <t>6788845</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6688088</t>
+          <t>6788845</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
